--- a/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -119,11 +119,7 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能产业指数</t>
+    <t>MA250</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -131,8 +127,8 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>MA250</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>单位：元</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -743,7 +739,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1076,6 +1072,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1085,7 +1084,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1417,6 +1416,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1460,7 +1462,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1793,6 +1795,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1802,7 +1807,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2131,6 +2136,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2174,7 +2182,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2507,6 +2515,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2516,7 +2527,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2848,6 +2859,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2870,11 +2884,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="442372480"/>
-        <c:axId val="442374016"/>
+        <c:axId val="469046016"/>
+        <c:axId val="469047936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="442372480"/>
+        <c:axId val="469046016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2917,14 +2931,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442374016"/>
+        <c:crossAx val="469047936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="442374016"/>
+        <c:axId val="469047936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2973,7 +2987,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442372480"/>
+        <c:crossAx val="469046016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3186,7 +3200,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3483,6 +3497,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3492,7 +3509,7 @@
               <c:f>'模型四 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3789,6 +3806,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>1179.7195080910908</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1212.9135345867317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3831,7 +3851,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4128,6 +4148,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4137,7 +4160,7 @@
               <c:f>'模型四 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4434,6 +4457,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>1725.915575606366</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1759.0798296952728</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4476,7 +4502,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4773,6 +4799,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4782,7 +4811,7 @@
               <c:f>'模型四 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5079,6 +5108,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>546.16629510854114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5100,11 +5132,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="450596224"/>
-        <c:axId val="450606208"/>
+        <c:axId val="482021376"/>
+        <c:axId val="482023296"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="450596224"/>
+        <c:axId val="482021376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5147,14 +5179,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="450606208"/>
+        <c:crossAx val="482023296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="450606208"/>
+        <c:axId val="482023296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5203,7 +5235,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="450596224"/>
+        <c:crossAx val="482021376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5416,7 +5448,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5713,6 +5745,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5722,7 +5757,7 @@
               <c:f>'模型四 (3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6019,6 +6054,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>250.30355595263484</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>255.16118173985649</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6061,7 +6099,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6358,6 +6396,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6367,7 +6408,7 @@
               <c:f>'模型四 (3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6664,6 +6705,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>380.48679167107468</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>385.34388479183116</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6706,7 +6750,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -7003,6 +7047,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7012,7 +7059,7 @@
               <c:f>'模型四 (3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="99"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7309,6 +7356,9 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>130.18270305197467</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7330,11 +7380,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="451266432"/>
-        <c:axId val="472383488"/>
+        <c:axId val="482090368"/>
+        <c:axId val="482100352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="451266432"/>
+        <c:axId val="482090368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7377,14 +7427,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472383488"/>
+        <c:crossAx val="482100352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472383488"/>
+        <c:axId val="482100352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7433,7 +7483,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="451266432"/>
+        <c:crossAx val="482090368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7541,7 +7591,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7584,7 +7634,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7627,7 +7677,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7940,7 +7990,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF114"/>
+  <dimension ref="A1:AF115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12624,6 +12674,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="115" spans="1:11" ht="12.75">
+      <c r="A115" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B115" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.1747980992467859</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I115" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J115" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K115" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12640,7 +12725,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF102"/>
+  <dimension ref="A1:AF103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12675,13 +12760,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>20</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -16779,6 +16864,41 @@
         <v>546.19606751527522</v>
       </c>
       <c r="K102" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="12.75">
+      <c r="A103" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B103" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C103" s="20">
+        <v>1.8694703600000002</v>
+      </c>
+      <c r="D103" s="21">
+        <v>33.194026495640955</v>
+      </c>
+      <c r="E103" s="22">
+        <v>19.263796983188126</v>
+      </c>
+      <c r="F103" s="22">
+        <v>19.53445522622572</v>
+      </c>
+      <c r="G103" s="22">
+        <v>33.66040583396633</v>
+      </c>
+      <c r="H103" s="22">
+        <v>1212.9135345867317</v>
+      </c>
+      <c r="I103" s="22">
+        <v>1759.0798296952728</v>
+      </c>
+      <c r="J103" s="22">
+        <v>546.16629510854114</v>
+      </c>
+      <c r="K103" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -16798,7 +16918,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AF102"/>
+  <dimension ref="A1:AF103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16833,13 +16953,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>23</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -16889,7 +17009,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -20937,6 +21057,41 @@
         <v>130.18323571843985</v>
       </c>
       <c r="K102" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="12.75">
+      <c r="A103" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B103" s="25">
+        <v>1.7231300000000001</v>
+      </c>
+      <c r="C103" s="20">
+        <v>1.8694703600000002</v>
+      </c>
+      <c r="D103" s="21">
+        <v>4.8576257872216422</v>
+      </c>
+      <c r="E103" s="22">
+        <v>2.8190709854866678</v>
+      </c>
+      <c r="F103" s="22">
+        <v>2.8239134078971615</v>
+      </c>
+      <c r="G103" s="22">
+        <v>4.8659699105498362</v>
+      </c>
+      <c r="H103" s="22">
+        <v>255.16118173985649</v>
+      </c>
+      <c r="I103" s="22">
+        <v>385.34388479183116</v>
+      </c>
+      <c r="J103" s="22">
+        <v>130.18270305197467</v>
+      </c>
+      <c r="K103" s="21">
         <v>380.47791488128132</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -123,7 +123,15 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>MA250</t>
+    <t>绝对收益率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能产业指数</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -739,7 +747,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1075,6 +1083,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1084,7 +1095,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1419,6 +1430,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1462,7 +1476,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1798,6 +1812,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1807,7 +1824,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2139,6 +2156,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2182,7 +2202,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2518,6 +2538,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2527,7 +2550,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2862,6 +2885,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2884,11 +2910,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="469046016"/>
-        <c:axId val="469047936"/>
+        <c:axId val="568725504"/>
+        <c:axId val="568727424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="469046016"/>
+        <c:axId val="568725504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2931,14 +2957,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469047936"/>
+        <c:crossAx val="568727424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="469047936"/>
+        <c:axId val="568727424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2987,7 +3013,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469046016"/>
+        <c:crossAx val="568725504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3200,7 +3226,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3500,6 +3526,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3509,7 +3538,7 @@
               <c:f>'模型四 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3809,6 +3838,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>1212.9135345867317</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1296.0589602077778</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3851,7 +3883,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4151,6 +4183,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4160,7 +4195,7 @@
               <c:f>'模型四 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4460,6 +4495,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>1759.0798296952728</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1840.562677832015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4502,7 +4540,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4802,6 +4840,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4811,7 +4852,7 @@
               <c:f>'模型四 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5111,6 +5152,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>546.16629510854114</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>544.5037176242372</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5132,11 +5176,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="482021376"/>
-        <c:axId val="482023296"/>
+        <c:axId val="568785920"/>
+        <c:axId val="568890112"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="482021376"/>
+        <c:axId val="568785920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5179,14 +5223,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="482023296"/>
+        <c:crossAx val="568890112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="482023296"/>
+        <c:axId val="568890112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5235,7 +5279,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="482021376"/>
+        <c:crossAx val="568785920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5448,7 +5492,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5748,6 +5792,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5757,7 +5804,7 @@
               <c:f>'模型四 (3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6057,6 +6104,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>255.16118173985649</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>274.41831749964462</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6099,7 +6149,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6399,6 +6449,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6408,7 +6461,7 @@
               <c:f>'模型四 (3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6708,6 +6761,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>385.34388479183116</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>404.36067728147316</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6750,7 +6806,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -7050,6 +7106,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7059,7 +7118,7 @@
               <c:f>'模型四 (3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="100"/>
+                <c:ptCount val="101"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7359,6 +7418,9 @@
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>130.18270305197467</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>129.94235978182854</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7380,11 +7442,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="482090368"/>
-        <c:axId val="482100352"/>
+        <c:axId val="92112000"/>
+        <c:axId val="92113536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="482090368"/>
+        <c:axId val="92112000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7427,14 +7489,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="482100352"/>
+        <c:crossAx val="92113536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="482100352"/>
+        <c:axId val="92113536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7483,7 +7545,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="482090368"/>
+        <c:crossAx val="92112000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7591,7 +7653,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7634,7 +7696,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7677,7 +7739,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7990,7 +8052,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF115"/>
+  <dimension ref="A1:AF116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12709,6 +12771,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="116" spans="1:11" ht="12.75">
+      <c r="A116" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B116" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.1794961447368402</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I116" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J116" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K116" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12725,7 +12822,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF103"/>
+  <dimension ref="A1:AF104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12883,7 +12980,7 @@
         <v>16</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>18</v>
@@ -16899,6 +16996,41 @@
         <v>546.16629510854114</v>
       </c>
       <c r="K103" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="12.75">
+      <c r="A104" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B104" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C104" s="20">
+        <v>1.8696278799999997</v>
+      </c>
+      <c r="D104" s="21">
+        <v>83.145425621046073</v>
+      </c>
+      <c r="E104" s="22">
+        <v>50.759713325262247</v>
+      </c>
+      <c r="F104" s="22">
+        <v>70.294168551487971</v>
+      </c>
+      <c r="G104" s="22">
+        <v>115.14325397070833</v>
+      </c>
+      <c r="H104" s="22">
+        <v>1296.0589602077778</v>
+      </c>
+      <c r="I104" s="22">
+        <v>1840.562677832015</v>
+      </c>
+      <c r="J104" s="22">
+        <v>544.5037176242372</v>
+      </c>
+      <c r="K104" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -16918,7 +17050,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AF103"/>
+  <dimension ref="A1:AF104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16953,13 +17085,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -17009,7 +17141,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -21092,6 +21224,41 @@
         <v>130.18270305197467</v>
       </c>
       <c r="K103" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="12.75">
+      <c r="A104" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B104" s="25">
+        <v>1.63802</v>
+      </c>
+      <c r="C104" s="20">
+        <v>1.8696278799999997</v>
+      </c>
+      <c r="D104" s="21">
+        <v>19.257135759788135</v>
+      </c>
+      <c r="E104" s="22">
+        <v>11.756349592671722</v>
+      </c>
+      <c r="F104" s="22">
+        <v>14.580263000568884</v>
+      </c>
+      <c r="G104" s="22">
+        <v>23.882762400191844</v>
+      </c>
+      <c r="H104" s="22">
+        <v>274.41831749964462</v>
+      </c>
+      <c r="I104" s="22">
+        <v>404.36067728147316</v>
+      </c>
+      <c r="J104" s="22">
+        <v>129.94235978182854</v>
+      </c>
+      <c r="K104" s="21">
         <v>380.47791488128132</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
@@ -123,15 +123,15 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>绝对收益率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>人工智能产业指数</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MA250</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -747,7 +747,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1086,6 +1086,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1095,7 +1098,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1433,6 +1436,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1476,7 +1482,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1815,6 +1821,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1824,7 +1833,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2159,6 +2168,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2202,7 +2214,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2541,6 +2553,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2550,7 +2565,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="114"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2888,6 +2903,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="112">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2910,11 +2928,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="568725504"/>
-        <c:axId val="568727424"/>
+        <c:axId val="428316928"/>
+        <c:axId val="428318720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="568725504"/>
+        <c:axId val="428316928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2957,14 +2975,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568727424"/>
+        <c:crossAx val="428318720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="568727424"/>
+        <c:axId val="428318720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3013,7 +3031,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568725504"/>
+        <c:crossAx val="428316928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3226,7 +3244,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3529,6 +3547,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3538,7 +3559,7 @@
               <c:f>'模型四 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3841,6 +3862,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>1296.0589602077778</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1313.9812666064583</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3883,7 +3907,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4186,6 +4210,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4195,7 +4222,7 @@
               <c:f>'模型四 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4498,6 +4525,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>1840.562677832015</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1866.9343432905844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4540,7 +4570,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4843,6 +4873,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4852,7 +4885,7 @@
               <c:f>'模型四 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5155,6 +5188,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>544.5037176242372</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>552.95307668412602</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5176,11 +5212,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="568785920"/>
-        <c:axId val="568890112"/>
+        <c:axId val="428493056"/>
+        <c:axId val="428527616"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="568785920"/>
+        <c:axId val="428493056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5223,14 +5259,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568890112"/>
+        <c:crossAx val="428527616"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="568890112"/>
+        <c:axId val="428527616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5279,7 +5315,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568785920"/>
+        <c:crossAx val="428493056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5492,7 +5528,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5795,6 +5831,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5804,7 +5843,7 @@
               <c:f>'模型四 (3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6107,6 +6146,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>274.41831749964462</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>276.34550955872504</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6149,7 +6191,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6452,6 +6494,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6461,7 +6506,7 @@
               <c:f>'模型四 (3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6764,6 +6809,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>404.36067728147316</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>408.04041695322195</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6806,7 +6854,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -7109,6 +7157,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7118,7 +7169,7 @@
               <c:f>'模型四 (3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="102"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7421,6 +7472,9 @@
                 </c:pt>
                 <c:pt idx="100">
                   <c:v>129.94235978182854</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>131.69490739449691</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7442,11 +7496,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="92112000"/>
-        <c:axId val="92113536"/>
+        <c:axId val="428586496"/>
+        <c:axId val="448806912"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="92112000"/>
+        <c:axId val="428586496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7489,14 +7543,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92113536"/>
+        <c:crossAx val="448806912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="92113536"/>
+        <c:axId val="448806912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7545,7 +7599,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92112000"/>
+        <c:crossAx val="428586496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7653,7 +7707,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7696,7 +7750,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7739,7 +7793,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8052,7 +8106,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF116"/>
+  <dimension ref="A1:AF117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12806,6 +12860,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="117" spans="1:11" ht="12.75">
+      <c r="A117" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B117" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C117" s="20">
+        <v>1.1845099478487591</v>
+      </c>
+      <c r="D117" s="21">
+        <v>0</v>
+      </c>
+      <c r="E117" s="22">
+        <v>0</v>
+      </c>
+      <c r="F117" s="22">
+        <v>0</v>
+      </c>
+      <c r="G117" s="22">
+        <v>0</v>
+      </c>
+      <c r="H117" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I117" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J117" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K117" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12822,7 +12911,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AF104"/>
+  <dimension ref="A1:AF105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12980,7 +13069,7 @@
         <v>16</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>18</v>
@@ -17031,6 +17120,41 @@
         <v>544.5037176242372</v>
       </c>
       <c r="K104" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="12.75">
+      <c r="A105" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B105" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C105" s="20">
+        <v>1.8657503599999992</v>
+      </c>
+      <c r="D105" s="21">
+        <v>17.922306398680565</v>
+      </c>
+      <c r="E105" s="22">
+        <v>10.193437908043682</v>
+      </c>
+      <c r="F105" s="22">
+        <v>80.487606459531648</v>
+      </c>
+      <c r="G105" s="22">
+        <v>141.51491942927774</v>
+      </c>
+      <c r="H105" s="22">
+        <v>1313.9812666064583</v>
+      </c>
+      <c r="I105" s="22">
+        <v>1866.9343432905844</v>
+      </c>
+      <c r="J105" s="22">
+        <v>552.95307668412602</v>
+      </c>
+      <c r="K105" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -17050,7 +17174,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AF104"/>
+  <dimension ref="A1:AF105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17085,13 +17209,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>23</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -21262,6 +21386,41 @@
         <v>380.47791488128132</v>
       </c>
     </row>
+    <row r="105" spans="1:11" ht="12.75">
+      <c r="A105" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B105" s="25">
+        <v>1.7582200000000001</v>
+      </c>
+      <c r="C105" s="20">
+        <v>1.8657503599999992</v>
+      </c>
+      <c r="D105" s="21">
+        <v>1.9271920590804075</v>
+      </c>
+      <c r="E105" s="22">
+        <v>1.0961040478895743</v>
+      </c>
+      <c r="F105" s="22">
+        <v>15.676367048458458</v>
+      </c>
+      <c r="G105" s="22">
+        <v>27.562502071940632</v>
+      </c>
+      <c r="H105" s="22">
+        <v>276.34550955872504</v>
+      </c>
+      <c r="I105" s="22">
+        <v>408.04041695322195</v>
+      </c>
+      <c r="J105" s="22">
+        <v>131.69490739449691</v>
+      </c>
+      <c r="K105" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
